--- a/AAII_Financials/Quarterly/CYAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CYAP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
   <si>
     <t>CYAP</t>
   </si>
@@ -656,129 +656,133 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43312</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42947</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42855</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42766</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -860,8 +864,11 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -943,8 +950,11 @@
       <c r="AC9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1026,8 +1036,11 @@
       <c r="AC10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,8 +1070,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1294,20 +1314,23 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>4</v>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,28 +1443,29 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
       </c>
       <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
         <v>100</v>
       </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
       <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
         <v>1300</v>
-      </c>
-      <c r="I17" s="3">
-        <v>100</v>
       </c>
       <c r="J17" s="3">
         <v>100</v>
@@ -1447,10 +1474,10 @@
         <v>100</v>
       </c>
       <c r="L17" s="3">
+        <v>100</v>
+      </c>
+      <c r="M17" s="3">
         <v>300</v>
-      </c>
-      <c r="M17" s="3">
-        <v>100</v>
       </c>
       <c r="N17" s="3">
         <v>100</v>
@@ -1465,7 +1492,7 @@
         <v>100</v>
       </c>
       <c r="R17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17" s="3">
         <v>0</v>
@@ -1500,8 +1527,11 @@
       <c r="AC17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1512,16 +1542,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
         <v>-100</v>
       </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
       <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-100</v>
       </c>
       <c r="J18" s="3">
         <v>-100</v>
@@ -1530,10 +1560,10 @@
         <v>-100</v>
       </c>
       <c r="L18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M18" s="3">
         <v>-300</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-100</v>
       </c>
       <c r="N18" s="3">
         <v>-100</v>
@@ -1548,7 +1578,7 @@
         <v>-100</v>
       </c>
       <c r="R18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S18" s="3">
         <v>0</v>
@@ -1583,8 +1613,11 @@
       <c r="AC18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,8 +1647,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1623,7 +1657,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1697,8 +1731,11 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1747,11 +1784,11 @@
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3">
+        <v>0</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
@@ -1780,16 +1817,19 @@
       <c r="AC21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>4</v>
@@ -1806,8 +1846,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1863,8 +1903,11 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1872,19 +1915,19 @@
         <v>100</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
         <v>-100</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>-1300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-100</v>
       </c>
       <c r="J23" s="3">
         <v>-100</v>
@@ -1893,10 +1936,10 @@
         <v>-100</v>
       </c>
       <c r="L23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M23" s="3">
         <v>-300</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-100</v>
       </c>
       <c r="N23" s="3">
         <v>-100</v>
@@ -1911,7 +1954,7 @@
         <v>-100</v>
       </c>
       <c r="R23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S23" s="3">
         <v>0</v>
@@ -1946,8 +1989,11 @@
       <c r="AC23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2029,8 +2075,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,8 +2161,11 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2121,19 +2173,19 @@
         <v>100</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
         <v>-100</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>-1300</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-100</v>
       </c>
       <c r="J26" s="3">
         <v>-100</v>
@@ -2142,10 +2194,10 @@
         <v>-100</v>
       </c>
       <c r="L26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M26" s="3">
         <v>-300</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-100</v>
       </c>
       <c r="N26" s="3">
         <v>-100</v>
@@ -2160,7 +2212,7 @@
         <v>-100</v>
       </c>
       <c r="R26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S26" s="3">
         <v>0</v>
@@ -2195,8 +2247,11 @@
       <c r="AC26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2204,31 +2259,31 @@
         <v>100</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
         <v>-100</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>-1300</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-100</v>
       </c>
       <c r="J27" s="3">
         <v>-100</v>
       </c>
       <c r="K27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>-300</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-100</v>
       </c>
       <c r="N27" s="3">
         <v>-100</v>
@@ -2243,7 +2298,7 @@
         <v>-100</v>
       </c>
       <c r="R27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S27" s="3">
         <v>0</v>
@@ -2278,8 +2333,11 @@
       <c r="AC27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,8 +2677,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2619,7 +2689,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -2693,8 +2763,11 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2702,31 +2775,31 @@
         <v>100</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
         <v>-100</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>-1300</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-100</v>
       </c>
       <c r="J33" s="3">
         <v>-100</v>
       </c>
       <c r="K33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
         <v>-300</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-100</v>
       </c>
       <c r="N33" s="3">
         <v>-100</v>
@@ -2741,7 +2814,7 @@
         <v>-100</v>
       </c>
       <c r="R33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S33" s="3">
         <v>0</v>
@@ -2776,8 +2849,11 @@
       <c r="AC33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,8 +2935,11 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2868,31 +2947,31 @@
         <v>100</v>
       </c>
       <c r="E35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
         <v>-100</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>-1300</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-100</v>
       </c>
       <c r="J35" s="3">
         <v>-100</v>
       </c>
       <c r="K35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>-300</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-100</v>
       </c>
       <c r="N35" s="3">
         <v>-100</v>
@@ -2907,7 +2986,7 @@
         <v>-100</v>
       </c>
       <c r="R35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S35" s="3">
         <v>0</v>
@@ -2942,96 +3021,102 @@
       <c r="AC35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43312</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42947</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42855</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42766</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,8 +3178,9 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3119,25 +3206,25 @@
         <v>0</v>
       </c>
       <c r="K41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L41" s="3">
         <v>100</v>
       </c>
       <c r="M41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
         <v>100</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
       <c r="P41" s="3">
         <v>0</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>4</v>
+      <c r="Q41" s="3">
+        <v>0</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>4</v>
@@ -3154,8 +3241,8 @@
       <c r="V41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
+      <c r="W41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X41" s="3">
         <v>0</v>
@@ -3175,8 +3262,11 @@
       <c r="AC41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,8 +3348,11 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3341,8 +3434,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3424,8 +3520,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3489,14 +3588,14 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>4</v>
+      <c r="X45" s="3">
+        <v>0</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
+      <c r="Z45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA45" s="3">
         <v>0</v>
@@ -3507,8 +3606,11 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3534,20 +3636,20 @@
         <v>0</v>
       </c>
       <c r="K46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3">
         <v>100</v>
       </c>
       <c r="M46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N46" s="3">
+        <v>0</v>
+      </c>
+      <c r="O46" s="3">
         <v>100</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3572,14 +3674,14 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>4</v>
+      <c r="X46" s="3">
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z46" s="3">
-        <v>0</v>
+      <c r="Z46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA46" s="3">
         <v>0</v>
@@ -3590,8 +3692,11 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3673,22 +3778,25 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
+      <c r="D48" s="3">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
       </c>
       <c r="H48" s="3">
         <v>0</v>
@@ -3696,32 +3804,32 @@
       <c r="I48" s="3">
         <v>0</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3">
         <v>500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>300</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3">
         <v>1400</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R48" s="3">
-        <v>1400</v>
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S48" s="3">
         <v>1400</v>
@@ -3729,23 +3837,23 @@
       <c r="T48" s="3">
         <v>1400</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>4</v>
+      <c r="U48" s="3">
+        <v>1400</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>4</v>
+      <c r="W48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z48" s="3">
-        <v>0</v>
+      <c r="Z48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
@@ -3756,8 +3864,11 @@
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3771,40 +3882,40 @@
         <v>500</v>
       </c>
       <c r="G49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H49" s="3">
         <v>400</v>
       </c>
       <c r="I49" s="3">
-        <v>1800</v>
+        <v>400</v>
       </c>
       <c r="J49" s="3">
         <v>1800</v>
       </c>
       <c r="K49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L49" s="3">
         <v>1600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1400</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1700</v>
       </c>
       <c r="N49" s="3">
         <v>1700</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1400</v>
+      <c r="O49" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q49" s="3">
         <v>1400</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>4</v>
+      <c r="R49" s="3">
+        <v>1400</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>4</v>
@@ -3812,12 +3923,12 @@
       <c r="T49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U49" s="3">
+      <c r="U49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V49" s="3">
         <v>1400</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3827,8 +3938,8 @@
       <c r="Y49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,8 +4122,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4025,11 +4145,11 @@
       <c r="H52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
@@ -4046,8 +4166,8 @@
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,8 +4294,11 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4186,31 +4312,31 @@
         <v>500</v>
       </c>
       <c r="G54" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H54" s="3">
         <v>400</v>
       </c>
       <c r="I54" s="3">
-        <v>1800</v>
+        <v>400</v>
       </c>
       <c r="J54" s="3">
         <v>1800</v>
       </c>
       <c r="K54" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L54" s="3">
         <v>2200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1800</v>
-      </c>
-      <c r="O54" s="3">
-        <v>1400</v>
       </c>
       <c r="P54" s="3">
         <v>1400</v>
@@ -4231,19 +4357,19 @@
         <v>1400</v>
       </c>
       <c r="V54" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="W54" s="3">
         <v>0</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>4</v>
+      <c r="X54" s="3">
+        <v>0</v>
       </c>
       <c r="Y54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z54" s="3">
-        <v>0</v>
+      <c r="Z54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA54" s="3">
         <v>0</v>
@@ -4254,8 +4380,11 @@
       <c r="AC54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,8 +4446,9 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4325,7 +4456,7 @@
         <v>0</v>
       </c>
       <c r="E57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
@@ -4337,25 +4468,25 @@
         <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>200</v>
       </c>
       <c r="K57" s="3">
+        <v>200</v>
+      </c>
+      <c r="L57" s="3">
         <v>300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>100</v>
       </c>
       <c r="P57" s="3">
         <v>100</v>
@@ -4381,14 +4512,14 @@
       <c r="W57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>4</v>
+      <c r="X57" s="3">
+        <v>100</v>
       </c>
       <c r="Y57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z57" s="3">
-        <v>100</v>
+      <c r="Z57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA57" s="3">
         <v>100</v>
@@ -4399,8 +4530,11 @@
       <c r="AC57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4428,29 +4562,29 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N58" s="3">
         <v>800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>300</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>200</v>
       </c>
       <c r="R58" s="3">
         <v>200</v>
       </c>
       <c r="S58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T58" s="3">
         <v>100</v>
@@ -4464,14 +4598,14 @@
       <c r="W58" s="3">
         <v>100</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>4</v>
+      <c r="X58" s="3">
+        <v>100</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z58" s="3">
-        <v>100</v>
+      <c r="Z58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA58" s="3">
         <v>100</v>
@@ -4482,8 +4616,11 @@
       <c r="AC58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4511,11 +4648,11 @@
       <c r="K59" s="3">
         <v>0</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -4565,8 +4702,11 @@
       <c r="AC59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4574,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="E60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F60" s="3">
         <v>100</v>
@@ -4586,37 +4726,37 @@
         <v>100</v>
       </c>
       <c r="I60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J60" s="3">
         <v>200</v>
       </c>
       <c r="K60" s="3">
+        <v>200</v>
+      </c>
+      <c r="L60" s="3">
         <v>300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>100</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>300</v>
       </c>
       <c r="R60" s="3">
         <v>300</v>
       </c>
       <c r="S60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T60" s="3">
         <v>200</v>
@@ -4630,14 +4770,14 @@
       <c r="W60" s="3">
         <v>200</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>4</v>
+      <c r="X60" s="3">
+        <v>200</v>
       </c>
       <c r="Y60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z60" s="3">
-        <v>200</v>
+      <c r="Z60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA60" s="3">
         <v>200</v>
@@ -4648,13 +4788,16 @@
       <c r="AC60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
         <v>200</v>
@@ -4663,38 +4806,38 @@
         <v>200</v>
       </c>
       <c r="G61" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H61" s="3">
         <v>100</v>
       </c>
       <c r="I61" s="3">
+        <v>100</v>
+      </c>
+      <c r="J61" s="3">
         <v>200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>500</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>100</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>300</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4731,40 +4874,43 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
@@ -4775,23 +4921,23 @@
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>4</v>
+      <c r="V62" s="3">
+        <v>0</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>4</v>
@@ -4802,8 +4948,8 @@
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,58 +5218,61 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>100</v>
+      </c>
+      <c r="E66" s="3">
         <v>200</v>
-      </c>
-      <c r="E66" s="3">
-        <v>300</v>
       </c>
       <c r="F66" s="3">
         <v>300</v>
       </c>
       <c r="G66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H66" s="3">
         <v>200</v>
       </c>
       <c r="I66" s="3">
+        <v>200</v>
+      </c>
+      <c r="J66" s="3">
         <v>400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>800</v>
-      </c>
-      <c r="M66" s="3">
-        <v>900</v>
       </c>
       <c r="N66" s="3">
         <v>900</v>
       </c>
       <c r="O66" s="3">
+        <v>900</v>
+      </c>
+      <c r="P66" s="3">
         <v>500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>400</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>300</v>
       </c>
       <c r="R66" s="3">
         <v>300</v>
       </c>
       <c r="S66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T66" s="3">
         <v>200</v>
@@ -5128,14 +5286,14 @@
       <c r="W66" s="3">
         <v>200</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>4</v>
+      <c r="X66" s="3">
+        <v>200</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z66" s="3">
-        <v>200</v>
+      <c r="Z66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA66" s="3">
         <v>200</v>
@@ -5146,8 +5304,11 @@
       <c r="AC66" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,58 +5680,61 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-10900</v>
+        <v>-10800</v>
       </c>
       <c r="E72" s="3">
         <v>-10900</v>
       </c>
       <c r="F72" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="G72" s="3">
         <v>-11000</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-10900</v>
       </c>
       <c r="H72" s="3">
         <v>-10900</v>
       </c>
       <c r="I72" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="J72" s="3">
         <v>-9600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-9500</v>
-      </c>
-      <c r="K72" s="3">
-        <v>-9400</v>
       </c>
       <c r="L72" s="3">
         <v>-9400</v>
       </c>
       <c r="M72" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="N72" s="3">
         <v>-9100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-9000</v>
-      </c>
-      <c r="O72" s="3">
-        <v>-8900</v>
       </c>
       <c r="P72" s="3">
         <v>-8900</v>
       </c>
       <c r="Q72" s="3">
-        <v>-8700</v>
+        <v>-8900</v>
       </c>
       <c r="R72" s="3">
         <v>-8700</v>
       </c>
       <c r="S72" s="3">
-        <v>-8600</v>
+        <v>-8700</v>
       </c>
       <c r="T72" s="3">
         <v>-8600</v>
@@ -5574,14 +5748,14 @@
       <c r="W72" s="3">
         <v>-8600</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>4</v>
+      <c r="X72" s="3">
+        <v>-8600</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z72" s="3">
-        <v>-8600</v>
+      <c r="Z72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA72" s="3">
         <v>-8600</v>
@@ -5592,8 +5766,11 @@
       <c r="AC72" s="3">
         <v>-8600</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3">
+        <v>-8600</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,16 +6024,19 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>400</v>
+      </c>
+      <c r="E76" s="3">
         <v>300</v>
-      </c>
-      <c r="E76" s="3">
-        <v>200</v>
       </c>
       <c r="F76" s="3">
         <v>200</v>
@@ -5862,22 +6048,22 @@
         <v>200</v>
       </c>
       <c r="I76" s="3">
+        <v>200</v>
+      </c>
+      <c r="J76" s="3">
         <v>1400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>800</v>
-      </c>
-      <c r="N76" s="3">
-        <v>900</v>
       </c>
       <c r="O76" s="3">
         <v>900</v>
@@ -5886,34 +6072,34 @@
         <v>900</v>
       </c>
       <c r="Q76" s="3">
+        <v>900</v>
+      </c>
+      <c r="R76" s="3">
         <v>1000</v>
-      </c>
-      <c r="R76" s="3">
-        <v>1100</v>
       </c>
       <c r="S76" s="3">
         <v>1100</v>
       </c>
       <c r="T76" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="U76" s="3">
         <v>1200</v>
       </c>
       <c r="V76" s="3">
-        <v>-200</v>
+        <v>1200</v>
       </c>
       <c r="W76" s="3">
         <v>-200</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>4</v>
+      <c r="X76" s="3">
+        <v>-200</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z76" s="3">
-        <v>-200</v>
+      <c r="Z76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA76" s="3">
         <v>-200</v>
@@ -5924,8 +6110,11 @@
       <c r="AC76" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,96 +6196,102 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43312</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42947</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42855</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42766</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6104,31 +6299,31 @@
         <v>100</v>
       </c>
       <c r="E81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
         <v>-100</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>-1300</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-100</v>
       </c>
       <c r="J81" s="3">
         <v>-100</v>
       </c>
       <c r="K81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
         <v>-300</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-100</v>
       </c>
       <c r="N81" s="3">
         <v>-100</v>
@@ -6143,7 +6338,7 @@
         <v>-100</v>
       </c>
       <c r="R81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S81" s="3">
         <v>0</v>
@@ -6178,8 +6373,11 @@
       <c r="AC81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,56 +6921,59 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
       </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>-200</v>
-      </c>
-      <c r="K89" s="3">
-        <v>100</v>
       </c>
       <c r="L89" s="3">
         <v>100</v>
       </c>
       <c r="M89" s="3">
+        <v>100</v>
+      </c>
+      <c r="N89" s="3">
         <v>-600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
@@ -6790,8 +7007,11 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7041,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6833,11 +7054,11 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
@@ -6845,16 +7066,16 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>4</v>
@@ -6865,8 +7086,8 @@
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -6904,8 +7125,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,8 +7297,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7082,11 +7312,11 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
@@ -7094,44 +7324,44 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>1300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1400</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
@@ -7153,8 +7383,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,68 +7759,71 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P100" s="3">
         <v>100</v>
       </c>
       <c r="Q100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-1400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1400</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -7599,8 +7845,11 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7682,8 +7931,11 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7706,11 +7958,11 @@
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
@@ -7718,11 +7970,11 @@
         <v>0</v>
       </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>100</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
         <v>0</v>
       </c>
@@ -7763,6 +8015,9 @@
         <v>0</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CYAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CYAP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
   <si>
     <t>CYAP</t>
   </si>
@@ -656,133 +656,137 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43312</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43220</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42947</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42855</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42766</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -867,8 +871,11 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -953,8 +960,11 @@
       <c r="AD9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1039,8 +1049,11 @@
       <c r="AD10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,8 +1084,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1157,8 +1171,11 @@
       <c r="AD12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,31 +1260,34 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1317,20 +1337,23 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>4</v>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1415,8 +1438,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,31 +1470,32 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>500</v>
+      </c>
+      <c r="E17" s="3">
         <v>-100</v>
       </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
       <c r="F17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
         <v>100</v>
       </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
       <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
         <v>1300</v>
-      </c>
-      <c r="J17" s="3">
-        <v>100</v>
       </c>
       <c r="K17" s="3">
         <v>100</v>
@@ -1477,10 +1504,10 @@
         <v>100</v>
       </c>
       <c r="M17" s="3">
+        <v>100</v>
+      </c>
+      <c r="N17" s="3">
         <v>300</v>
-      </c>
-      <c r="N17" s="3">
-        <v>100</v>
       </c>
       <c r="O17" s="3">
         <v>100</v>
@@ -1495,7 +1522,7 @@
         <v>100</v>
       </c>
       <c r="S17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T17" s="3">
         <v>0</v>
@@ -1530,8 +1557,11 @@
       <c r="AD17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1539,22 +1569,22 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
       <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-100</v>
       </c>
       <c r="K18" s="3">
         <v>-100</v>
@@ -1563,10 +1593,10 @@
         <v>-100</v>
       </c>
       <c r="M18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N18" s="3">
         <v>-300</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-100</v>
       </c>
       <c r="O18" s="3">
         <v>-100</v>
@@ -1581,7 +1611,7 @@
         <v>-100</v>
       </c>
       <c r="S18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T18" s="3">
         <v>0</v>
@@ -1616,8 +1646,11 @@
       <c r="AD18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,8 +1681,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1657,7 +1691,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1734,8 +1768,11 @@
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1787,11 +1824,11 @@
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3">
+        <v>0</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
@@ -1820,19 +1857,22 @@
       <c r="AD21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>4</v>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>4</v>
@@ -1849,8 +1889,8 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1906,31 +1946,34 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="E23" s="3">
         <v>100</v>
       </c>
       <c r="F23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-100</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-100</v>
       </c>
       <c r="K23" s="3">
         <v>-100</v>
@@ -1939,10 +1982,10 @@
         <v>-100</v>
       </c>
       <c r="M23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N23" s="3">
         <v>-300</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-100</v>
       </c>
       <c r="O23" s="3">
         <v>-100</v>
@@ -1957,7 +2000,7 @@
         <v>-100</v>
       </c>
       <c r="S23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T23" s="3">
         <v>0</v>
@@ -1992,8 +2035,11 @@
       <c r="AD23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2078,8 +2124,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,31 +2213,34 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="E26" s="3">
         <v>100</v>
       </c>
       <c r="F26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-100</v>
       </c>
       <c r="K26" s="3">
         <v>-100</v>
@@ -2197,10 +2249,10 @@
         <v>-100</v>
       </c>
       <c r="M26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N26" s="3">
         <v>-300</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-100</v>
       </c>
       <c r="O26" s="3">
         <v>-100</v>
@@ -2215,7 +2267,7 @@
         <v>-100</v>
       </c>
       <c r="S26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T26" s="3">
         <v>0</v>
@@ -2250,43 +2302,46 @@
       <c r="AD26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="E27" s="3">
         <v>100</v>
       </c>
       <c r="F27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-100</v>
       </c>
       <c r="K27" s="3">
         <v>-100</v>
       </c>
       <c r="L27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>-300</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-100</v>
       </c>
       <c r="O27" s="3">
         <v>-100</v>
@@ -2301,7 +2356,7 @@
         <v>-100</v>
       </c>
       <c r="S27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T27" s="3">
         <v>0</v>
@@ -2336,8 +2391,11 @@
       <c r="AD27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2480,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2569,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2658,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,8 +2747,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2689,7 +2759,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -2766,43 +2836,46 @@
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="E33" s="3">
         <v>100</v>
       </c>
       <c r="F33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-100</v>
       </c>
       <c r="K33" s="3">
         <v>-100</v>
       </c>
       <c r="L33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>-300</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-100</v>
       </c>
       <c r="O33" s="3">
         <v>-100</v>
@@ -2817,7 +2890,7 @@
         <v>-100</v>
       </c>
       <c r="S33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T33" s="3">
         <v>0</v>
@@ -2852,8 +2925,11 @@
       <c r="AD33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,43 +3014,46 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="E35" s="3">
         <v>100</v>
       </c>
       <c r="F35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-100</v>
       </c>
       <c r="K35" s="3">
         <v>-100</v>
       </c>
       <c r="L35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>-300</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-100</v>
       </c>
       <c r="O35" s="3">
         <v>-100</v>
@@ -2989,7 +3068,7 @@
         <v>-100</v>
       </c>
       <c r="S35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T35" s="3">
         <v>0</v>
@@ -3024,99 +3103,105 @@
       <c r="AD35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43312</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43220</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42947</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42855</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42766</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3232,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,8 +3265,9 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3209,25 +3296,25 @@
         <v>0</v>
       </c>
       <c r="L41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M41" s="3">
         <v>100</v>
       </c>
       <c r="N41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3">
         <v>100</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
       <c r="Q41" s="3">
         <v>0</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>4</v>
+      <c r="R41" s="3">
+        <v>0</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>4</v>
@@ -3244,8 +3331,8 @@
       <c r="W41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
+      <c r="X41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y41" s="3">
         <v>0</v>
@@ -3265,8 +3352,11 @@
       <c r="AD41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3351,8 +3441,11 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3437,8 +3530,11 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3523,8 +3619,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3534,8 +3633,8 @@
       <c r="E45" s="3">
         <v>0</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
@@ -3591,14 +3690,14 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>4</v>
+      <c r="Y45" s="3">
+        <v>0</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
+      <c r="AA45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB45" s="3">
         <v>0</v>
@@ -3609,8 +3708,11 @@
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3639,20 +3741,20 @@
         <v>0</v>
       </c>
       <c r="L46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M46" s="3">
         <v>100</v>
       </c>
       <c r="N46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3">
         <v>100</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3677,14 +3779,14 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>4</v>
+      <c r="Y46" s="3">
+        <v>0</v>
       </c>
       <c r="Z46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA46" s="3">
-        <v>0</v>
+      <c r="AA46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB46" s="3">
         <v>0</v>
@@ -3695,8 +3797,11 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3781,8 +3886,11 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3807,32 +3915,32 @@
       <c r="J48" s="3">
         <v>0</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="K48" s="3">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="3">
         <v>500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q48" s="3">
         <v>1400</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S48" s="3">
-        <v>1400</v>
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T48" s="3">
         <v>1400</v>
@@ -3840,23 +3948,23 @@
       <c r="U48" s="3">
         <v>1400</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>4</v>
+      <c r="V48" s="3">
+        <v>1400</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3" t="s">
-        <v>4</v>
+      <c r="X48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>0</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
+      <c r="AA48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB48" s="3">
         <v>0</v>
@@ -3867,58 +3975,61 @@
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
         <v>500</v>
       </c>
-      <c r="F49" s="3">
-        <v>500</v>
+      <c r="F49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G49" s="3">
         <v>500</v>
       </c>
       <c r="H49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I49" s="3">
         <v>400</v>
       </c>
       <c r="J49" s="3">
-        <v>1800</v>
+        <v>400</v>
       </c>
       <c r="K49" s="3">
         <v>1800</v>
       </c>
       <c r="L49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M49" s="3">
         <v>1600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1400</v>
-      </c>
-      <c r="N49" s="3">
-        <v>1700</v>
       </c>
       <c r="O49" s="3">
         <v>1700</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>1400</v>
+      <c r="P49" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R49" s="3">
         <v>1400</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>4</v>
+      <c r="S49" s="3">
+        <v>1400</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>4</v>
@@ -3926,12 +4037,12 @@
       <c r="U49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V49" s="3">
+      <c r="V49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W49" s="3">
         <v>1400</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3941,8 +4052,8 @@
       <c r="Z49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
+      <c r="AA49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB49" s="3">
         <v>0</v>
@@ -3953,8 +4064,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4153,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,13 +4242,16 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3">
+        <v>0</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>4</v>
@@ -4148,11 +4268,11 @@
       <c r="I52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
@@ -4169,8 +4289,8 @@
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -4211,8 +4331,11 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,49 +4420,52 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E54" s="3">
         <v>500</v>
       </c>
       <c r="F54" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G54" s="3">
         <v>500</v>
       </c>
       <c r="H54" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I54" s="3">
         <v>400</v>
       </c>
       <c r="J54" s="3">
-        <v>1800</v>
+        <v>400</v>
       </c>
       <c r="K54" s="3">
         <v>1800</v>
       </c>
       <c r="L54" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M54" s="3">
         <v>2200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1800</v>
-      </c>
-      <c r="P54" s="3">
-        <v>1400</v>
       </c>
       <c r="Q54" s="3">
         <v>1400</v>
@@ -4360,19 +4486,19 @@
         <v>1400</v>
       </c>
       <c r="W54" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="X54" s="3">
         <v>0</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>4</v>
+      <c r="Y54" s="3">
+        <v>0</v>
       </c>
       <c r="Z54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA54" s="3">
-        <v>0</v>
+      <c r="AA54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB54" s="3">
         <v>0</v>
@@ -4383,8 +4509,11 @@
       <c r="AD54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4544,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,8 +4577,9 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4471,25 +4602,25 @@
         <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
       </c>
       <c r="L57" s="3">
+        <v>200</v>
+      </c>
+      <c r="M57" s="3">
         <v>300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
-      </c>
-      <c r="P57" s="3">
-        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
@@ -4515,14 +4646,14 @@
       <c r="X57" s="3">
         <v>100</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>4</v>
+      <c r="Y57" s="3">
+        <v>100</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA57" s="3">
-        <v>100</v>
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB57" s="3">
         <v>100</v>
@@ -4533,8 +4664,11 @@
       <c r="AD57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4565,29 +4699,29 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O58" s="3">
         <v>800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>300</v>
-      </c>
-      <c r="R58" s="3">
-        <v>200</v>
       </c>
       <c r="S58" s="3">
         <v>200</v>
       </c>
       <c r="T58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U58" s="3">
         <v>100</v>
@@ -4601,14 +4735,14 @@
       <c r="X58" s="3">
         <v>100</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>4</v>
+      <c r="Y58" s="3">
+        <v>100</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA58" s="3">
-        <v>100</v>
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB58" s="3">
         <v>100</v>
@@ -4619,8 +4753,11 @@
       <c r="AD58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4651,11 +4788,11 @@
       <c r="L59" s="3">
         <v>0</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N59" s="3">
-        <v>0</v>
+      <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O59" s="3">
         <v>0</v>
@@ -4705,8 +4842,11 @@
       <c r="AD59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4729,37 +4869,37 @@
         <v>100</v>
       </c>
       <c r="J60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K60" s="3">
         <v>200</v>
       </c>
       <c r="L60" s="3">
+        <v>200</v>
+      </c>
+      <c r="M60" s="3">
         <v>300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>100</v>
-      </c>
-      <c r="R60" s="3">
-        <v>300</v>
       </c>
       <c r="S60" s="3">
         <v>300</v>
       </c>
       <c r="T60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U60" s="3">
         <v>200</v>
@@ -4773,14 +4913,14 @@
       <c r="X60" s="3">
         <v>200</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>4</v>
+      <c r="Y60" s="3">
+        <v>200</v>
       </c>
       <c r="Z60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA60" s="3">
-        <v>200</v>
+      <c r="AA60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB60" s="3">
         <v>200</v>
@@ -4791,8 +4931,11 @@
       <c r="AD60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4800,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>200</v>
@@ -4809,38 +4952,38 @@
         <v>200</v>
       </c>
       <c r="H61" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I61" s="3">
         <v>100</v>
       </c>
       <c r="J61" s="3">
+        <v>100</v>
+      </c>
+      <c r="K61" s="3">
         <v>200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>500</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>300</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4877,17 +5020,20 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3">
         <v>100</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4903,17 +5049,17 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
+        <v>0</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
@@ -4924,23 +5070,23 @@
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
+      <c r="R62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>4</v>
+      <c r="W62" s="3">
+        <v>0</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>4</v>
@@ -4951,8 +5097,8 @@
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -4963,8 +5109,11 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5198,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5287,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,16 +5376,19 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3">
         <v>100</v>
-      </c>
-      <c r="E66" s="3">
-        <v>200</v>
       </c>
       <c r="F66" s="3">
         <v>300</v>
@@ -5239,43 +5397,43 @@
         <v>300</v>
       </c>
       <c r="H66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I66" s="3">
         <v>200</v>
       </c>
       <c r="J66" s="3">
+        <v>200</v>
+      </c>
+      <c r="K66" s="3">
         <v>400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>800</v>
-      </c>
-      <c r="N66" s="3">
-        <v>900</v>
       </c>
       <c r="O66" s="3">
         <v>900</v>
       </c>
       <c r="P66" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q66" s="3">
         <v>500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>400</v>
-      </c>
-      <c r="R66" s="3">
-        <v>300</v>
       </c>
       <c r="S66" s="3">
         <v>300</v>
       </c>
       <c r="T66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U66" s="3">
         <v>200</v>
@@ -5289,14 +5447,14 @@
       <c r="X66" s="3">
         <v>200</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>4</v>
+      <c r="Y66" s="3">
+        <v>200</v>
       </c>
       <c r="Z66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA66" s="3">
-        <v>200</v>
+      <c r="AA66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB66" s="3">
         <v>200</v>
@@ -5307,8 +5465,11 @@
       <c r="AD66" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5500,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5587,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5676,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5765,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,61 +5854,64 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="G72" s="3">
         <v>-10900</v>
       </c>
-      <c r="F72" s="3">
-        <v>-10900</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11000</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-10900</v>
       </c>
       <c r="I72" s="3">
         <v>-10900</v>
       </c>
       <c r="J72" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="K72" s="3">
         <v>-9600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-9500</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-9400</v>
       </c>
       <c r="M72" s="3">
         <v>-9400</v>
       </c>
       <c r="N72" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="O72" s="3">
         <v>-9100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-9000</v>
-      </c>
-      <c r="P72" s="3">
-        <v>-8900</v>
       </c>
       <c r="Q72" s="3">
         <v>-8900</v>
       </c>
       <c r="R72" s="3">
-        <v>-8700</v>
+        <v>-8900</v>
       </c>
       <c r="S72" s="3">
         <v>-8700</v>
       </c>
       <c r="T72" s="3">
-        <v>-8600</v>
+        <v>-8700</v>
       </c>
       <c r="U72" s="3">
         <v>-8600</v>
@@ -5751,14 +5925,14 @@
       <c r="X72" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>4</v>
+      <c r="Y72" s="3">
+        <v>-8600</v>
       </c>
       <c r="Z72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA72" s="3">
-        <v>-8600</v>
+      <c r="AA72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB72" s="3">
         <v>-8600</v>
@@ -5769,8 +5943,11 @@
       <c r="AD72" s="3">
         <v>-8600</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3">
+        <v>-8600</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6032,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6121,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,19 +6210,22 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>0</v>
+      </c>
+      <c r="E76" s="3">
         <v>400</v>
       </c>
-      <c r="E76" s="3">
-        <v>300</v>
-      </c>
       <c r="F76" s="3">
-        <v>200</v>
+        <v>-300</v>
       </c>
       <c r="G76" s="3">
         <v>200</v>
@@ -6051,22 +6237,22 @@
         <v>200</v>
       </c>
       <c r="J76" s="3">
+        <v>200</v>
+      </c>
+      <c r="K76" s="3">
         <v>1400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>800</v>
-      </c>
-      <c r="O76" s="3">
-        <v>900</v>
       </c>
       <c r="P76" s="3">
         <v>900</v>
@@ -6075,34 +6261,34 @@
         <v>900</v>
       </c>
       <c r="R76" s="3">
+        <v>900</v>
+      </c>
+      <c r="S76" s="3">
         <v>1000</v>
-      </c>
-      <c r="S76" s="3">
-        <v>1100</v>
       </c>
       <c r="T76" s="3">
         <v>1100</v>
       </c>
       <c r="U76" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="V76" s="3">
         <v>1200</v>
       </c>
       <c r="W76" s="3">
-        <v>-200</v>
+        <v>1200</v>
       </c>
       <c r="X76" s="3">
         <v>-200</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>4</v>
+      <c r="Y76" s="3">
+        <v>-200</v>
       </c>
       <c r="Z76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA76" s="3">
-        <v>-200</v>
+      <c r="AA76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB76" s="3">
         <v>-200</v>
@@ -6113,8 +6299,11 @@
       <c r="AD76" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,134 +6388,140 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43312</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43220</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42947</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42855</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42766</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="E81" s="3">
         <v>100</v>
       </c>
       <c r="F81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-100</v>
       </c>
       <c r="K81" s="3">
         <v>-100</v>
       </c>
       <c r="L81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>-300</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-100</v>
       </c>
       <c r="O81" s="3">
         <v>-100</v>
@@ -6341,7 +6536,7 @@
         <v>-100</v>
       </c>
       <c r="S81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T81" s="3">
         <v>0</v>
@@ -6376,8 +6571,11 @@
       <c r="AD81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,8 +6606,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6494,8 +6693,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6782,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6871,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6960,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7049,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,59 +7138,62 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
         <v>100</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
         <v>0</v>
       </c>
       <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>-200</v>
-      </c>
-      <c r="L89" s="3">
-        <v>100</v>
       </c>
       <c r="M89" s="3">
         <v>100</v>
       </c>
       <c r="N89" s="3">
+        <v>100</v>
+      </c>
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
@@ -7010,8 +7227,11 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,8 +7262,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7057,11 +7278,11 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -7069,16 +7290,16 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>4</v>
@@ -7089,8 +7310,8 @@
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -7128,8 +7349,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7438,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,8 +7527,11 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7315,11 +7545,11 @@
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
@@ -7327,44 +7557,44 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>1300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1400</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
@@ -7386,8 +7616,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7651,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7504,8 +7738,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7827,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7916,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,71 +8005,74 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="3">
         <v>100</v>
       </c>
       <c r="R100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-1400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
@@ -7848,8 +8094,11 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7934,8 +8183,11 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7961,11 +8213,11 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
@@ -7973,11 +8225,11 @@
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>100</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
         <v>0</v>
       </c>
@@ -8018,6 +8270,9 @@
         <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>0</v>
       </c>
     </row>
